--- a/agentes/02_CFO_Finanzas/BANCO BCI/CARTOLAS MOVIMIENTOS MES/cuenta abril the boos 09042026.xlsx
+++ b/agentes/02_CFO_Finanzas/BANCO BCI/CARTOLAS MOVIMIENTOS MES/cuenta abril the boos 09042026.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
   <si>
     <t>Mis Movimientos</t>
   </si>
@@ -109,138 +109,6 @@
   </si>
   <si>
     <t>Transferencia recibida de Patricia Veronica Lobo</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de Jorge Alexis Ramirez Gomez</t>
-  </si>
-  <si>
-    <t>Pago en línea Tesoreria</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a beatriz Rojas</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a Angelica Becerra Ampuero</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a RUBEN SANTIAGO ROJAS VILLABLANCA</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a GABRIELA SANCHEZ</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a joaquin Ortubia</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a GERALDINE LASTRA</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a Daphne Urriola</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a NICOLAS MILLAN</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a Rodrigo Aguilera</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a VIVIANA ALEJANDRA POBLETE GONZ</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de DIAZ ARROYO FERNANDA ROSA</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de ANDREA ALEJANDRA LUENGO VASQUE</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de SANTIS PALLERES ERICK ALEJANDR</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de CAMBARERI  SANDRA RAQUEL</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de MUNOZ MARTINEZ FRANCISCA MACAR</t>
-  </si>
-  <si>
-    <t>Pago en línea Servipag (www.servipag.com)</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de ROSA VERONICA MORAN MENA</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de LEONARDO ANDRES URRA DEVIA</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de Marcelo Adolfo Ruiz</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a vladimir palma</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a wittan asociados</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de DANITZA JOHANA SILVA HUIRCAN</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de Ruth Mary Andreina Delgado Lop</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de FRANCISCA ANTONIA REYES TRONCO</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de Deisy Clarivel Garrido</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de STEFANY ALEJANDRA LEIVA CALDER</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de URRUTIA GEHRMANN LUIS HUMBERTO</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de CRISTI ROJAS MAURICIO IGNACIO</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de BARBARA ANTONIA NORAMBUENA ARA</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de VIVIANA ELIZABETH FERNANDEZ MARCHANT</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de MARTINA IGNACIA FERNANDEZ MARC</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a SEBASTIAN MARTINEZ VALLEJOS</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a CAMILO MEDINA</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a ESIF STRENGTH SPA</t>
-  </si>
-  <si>
-    <t>Transferencia enviada a RUBEN</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de Gina Carolina Belmar</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de OCARES CONTRERAS MONICA NOEMI</t>
-  </si>
-  <si>
-    <t>Pago en línea SII</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de ROJAS BELLO FABIAN EDUARDO</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de ALVAREZ VENEGAS KATHERINNE ING</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de Cristian Ivan Vidal</t>
-  </si>
-  <si>
-    <t>Transferencia recibida de PAULINA ARLET VALLEJOS VALLEJO</t>
   </si>
 </sst>
 </file>
@@ -263,11 +131,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -605,7 +475,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:F928"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1264,1396 +1134,85 @@
         <v>-669084</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B34" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F34" s="10">
-        <v>-689084</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B35" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="10">
-        <v>720000</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="10">
-        <v>-726984</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B36" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" s="10">
-        <v>891058</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="10">
-        <v>-6984</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B37" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="10">
-        <v>100000</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="10">
-        <v>884074</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B38" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="10">
-        <v>60000</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="10">
-        <v>984074</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B39" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="10">
-        <v>60000</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="10">
-        <v>1044074</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B40" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="10">
-        <v>385000</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="10">
-        <v>1104074</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B41" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="10">
-        <v>960000</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="10">
-        <v>1489074</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B42" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="10">
-        <v>651000</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="10">
-        <v>2449074</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B43" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="10">
-        <v>252000</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="10">
-        <v>3100074</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B44" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="10">
-        <v>315000</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="10">
-        <v>3352074</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B45" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="10">
-        <v>224000</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="10">
-        <v>3667074</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B46" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D46" s="10">
-        <v>35000</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="10">
-        <v>3891074</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B47" s="8">
-        <v>46113</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="10">
-        <v>42900</v>
-      </c>
-      <c r="F47" s="10">
-        <v>3926074</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B48" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="10">
-        <v>39900</v>
-      </c>
-      <c r="F48" s="10">
-        <v>3883174</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B49" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="10">
-        <v>27000</v>
-      </c>
-      <c r="F49" s="10">
-        <v>3843274</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B50" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="10">
-        <v>86000</v>
-      </c>
-      <c r="F50" s="10">
-        <v>3816274</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B51" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="10">
-        <v>201943</v>
-      </c>
-      <c r="F51" s="10">
-        <v>3730274</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8">
-        <v>46111</v>
-      </c>
-      <c r="B52" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="10">
-        <v>47900</v>
-      </c>
-      <c r="F52" s="10">
-        <v>3528331</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
-        <v>46111</v>
-      </c>
-      <c r="B53" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" s="10">
-        <v>122581</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="10">
-        <v>3480431</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8">
-        <v>46111</v>
-      </c>
-      <c r="B54" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" s="10">
-        <v>112511</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" s="10">
-        <v>3603012</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8">
-        <v>46111</v>
-      </c>
-      <c r="B55" s="8">
-        <v>46111</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="10">
-        <v>172147</v>
-      </c>
-      <c r="F55" s="10">
-        <v>3715523</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
-        <v>46110</v>
-      </c>
-      <c r="B56" s="8">
-        <v>46111</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="10">
-        <v>2000</v>
-      </c>
-      <c r="F56" s="10">
-        <v>3543376</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="8">
-        <v>46109</v>
-      </c>
-      <c r="B57" s="8">
-        <v>46111</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="10">
-        <v>5000</v>
-      </c>
-      <c r="F57" s="10">
-        <v>3541376</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="8">
-        <v>46109</v>
-      </c>
-      <c r="B58" s="8">
-        <v>46111</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="10">
-        <v>5000</v>
-      </c>
-      <c r="F58" s="10">
-        <v>3536376</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="8">
-        <v>46108</v>
-      </c>
-      <c r="B59" s="8">
-        <v>46108</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="10">
-        <v>158779</v>
-      </c>
-      <c r="F59" s="10">
-        <v>3531376</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
-        <v>46107</v>
-      </c>
-      <c r="B60" s="8">
-        <v>46108</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D60" s="10">
-        <v>18990</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="10">
-        <v>3372597</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="8">
-        <v>46107</v>
-      </c>
-      <c r="B61" s="8">
-        <v>46108</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="10">
-        <v>28949</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="10">
-        <v>3391587</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="8">
-        <v>46107</v>
-      </c>
-      <c r="B62" s="8">
-        <v>46107</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D62" s="10">
-        <v>116677</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="10">
-        <v>3420536</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="8">
-        <v>46107</v>
-      </c>
-      <c r="B63" s="8">
-        <v>46107</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="10">
-        <v>51326</v>
-      </c>
-      <c r="F63" s="10">
-        <v>3537213</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8">
-        <v>46107</v>
-      </c>
-      <c r="B64" s="8">
-        <v>46107</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F64" s="10">
-        <v>3485887</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="8">
-        <v>46106</v>
-      </c>
-      <c r="B65" s="8">
-        <v>46107</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="10">
-        <v>42900</v>
-      </c>
-      <c r="F65" s="10">
-        <v>3447987</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="8">
-        <v>46106</v>
-      </c>
-      <c r="B66" s="8">
-        <v>46106</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="10">
-        <v>210956</v>
-      </c>
-      <c r="F66" s="10">
-        <v>3405087</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B67" s="8">
-        <v>46106</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="10">
-        <v>76000</v>
-      </c>
-      <c r="F67" s="10">
-        <v>3194131</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B68" s="8">
-        <v>46105</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="10">
-        <v>3000</v>
-      </c>
-      <c r="F68" s="10">
-        <v>3118131</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B69" s="8">
-        <v>46105</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="10">
-        <v>34900</v>
-      </c>
-      <c r="F69" s="10">
-        <v>3115131</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B70" s="8">
-        <v>46105</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="10">
-        <v>63000</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="10">
-        <v>3080231</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B71" s="8">
-        <v>46105</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E71" s="10">
-        <v>340433</v>
-      </c>
-      <c r="F71" s="10">
-        <v>3143231</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="8">
-        <v>46104</v>
-      </c>
-      <c r="B72" s="8">
-        <v>46104</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" s="10">
-        <v>307471</v>
-      </c>
-      <c r="F72" s="10">
-        <v>2802798</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="8">
-        <v>46102</v>
-      </c>
-      <c r="B73" s="8">
-        <v>46104</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="10">
-        <v>5000</v>
-      </c>
-      <c r="F73" s="10">
-        <v>2495327</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="8">
-        <v>46102</v>
-      </c>
-      <c r="B74" s="8">
-        <v>46104</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="10">
-        <v>5000</v>
-      </c>
-      <c r="F74" s="10">
-        <v>2490327</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="8">
-        <v>46101</v>
-      </c>
-      <c r="B75" s="8">
-        <v>46104</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="10">
-        <v>42900</v>
-      </c>
-      <c r="F75" s="10">
-        <v>2485327</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="8">
-        <v>46101</v>
-      </c>
-      <c r="B76" s="8">
-        <v>46101</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="10">
-        <v>124241</v>
-      </c>
-      <c r="F76" s="10">
-        <v>2442427</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="8">
-        <v>46101</v>
-      </c>
-      <c r="B77" s="8">
-        <v>46101</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F77" s="10">
-        <v>2318186</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
-        <v>46100</v>
-      </c>
-      <c r="B78" s="8">
-        <v>46101</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F78" s="10">
-        <v>2280286</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="8">
-        <v>46100</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46101</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F79" s="10">
-        <v>2242386</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
-        <v>46100</v>
-      </c>
-      <c r="B80" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" s="10">
-        <v>37990</v>
-      </c>
-      <c r="F80" s="10">
-        <v>2204486</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="8">
-        <v>46100</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="10">
-        <v>109444</v>
-      </c>
-      <c r="F81" s="10">
-        <v>2166496</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B82" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F82" s="10">
-        <v>2057052</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B83" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D83" s="10">
-        <v>150000</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="10">
-        <v>2019152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B84" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D84" s="10">
-        <v>40000</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="10">
-        <v>2169152</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B85" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D85" s="10">
-        <v>40000</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="10">
-        <v>2209152</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B86" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D86" s="10">
-        <v>50000</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="10">
-        <v>2249152</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B87" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D87" s="10">
-        <v>40000</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" s="10">
-        <v>2299152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B88" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D88" s="10">
-        <v>150000</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="10">
-        <v>2339152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B89" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D89" s="10">
-        <v>150000</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="10">
-        <v>2489152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B90" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F90" s="10">
-        <v>2639152</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B91" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F91" s="10">
-        <v>2601252</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B92" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D92" s="10">
-        <v>13252</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" s="10">
-        <v>2563352</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B93" s="8">
-        <v>46100</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D93" s="10">
-        <v>15500</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" s="10">
-        <v>2576604</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B94" s="8">
-        <v>46099</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="10">
-        <v>37900</v>
-      </c>
-      <c r="F94" s="10">
-        <v>2592104</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="8">
-        <v>46099</v>
-      </c>
-      <c r="B95" s="8">
-        <v>46099</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="10">
-        <v>122910</v>
-      </c>
-      <c r="F95" s="10">
-        <v>2554204</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B96" s="8">
-        <v>46099</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="10">
-        <v>39900</v>
-      </c>
-      <c r="F96" s="10">
-        <v>2431294</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B97" s="8">
-        <v>46099</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="10">
-        <v>42900</v>
-      </c>
-      <c r="F97" s="10">
-        <v>2391394</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B98" s="8">
-        <v>46099</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="10">
-        <v>63000</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" s="10">
-        <v>2348494</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B99" s="8">
-        <v>46099</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E99" s="10">
-        <v>52900</v>
-      </c>
-      <c r="F99" s="10">
-        <v>2411494</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B100" s="8">
-        <v>46098</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="10">
-        <v>131152</v>
-      </c>
-      <c r="F100" s="10">
-        <v>2358594</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="8">
-        <v>46097</v>
-      </c>
-      <c r="B101" s="8">
-        <v>46098</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="10">
-        <v>39900</v>
-      </c>
-      <c r="F101" s="10">
-        <v>2227442</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="8">
-        <v>46097</v>
-      </c>
-      <c r="B102" s="8">
-        <v>46097</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E102" s="10">
-        <v>232461</v>
-      </c>
-      <c r="F102" s="10">
-        <v>2187542</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3470,78 +2029,6 @@
     <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
